--- a/week-02/Ex2A_events_normalized.xlsx
+++ b/week-02/Ex2A_events_normalized.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\patri\Documents\DataAnalytics\week-02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379AC158-9AE1-4103-A9BE-62D922887694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5E6797-EF03-4690-B45D-AE7C231E975D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="5235" windowWidth="29040" windowHeight="15720" xr2:uid="{5091876E-AF08-41C4-B976-D2AB9D8B455C}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="138">
   <si>
     <t>Event ID</t>
   </si>
@@ -446,14 +446,14 @@
     <t>EVENTS</t>
   </si>
   <si>
-    <t>The AI feedback assited with me identifyng the repeating values and redundant data but the formatting was a bit spotty and I had to make some changes to make sur ethe data stayed legit.</t>
+    <t>The AI feedback assited with me identifyng the repeating values and redundant data but the formatting was a bit spotty and I had to make some changes to make sure the data stayed legit.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -588,14 +588,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="35">
     <fill>
@@ -915,7 +907,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="43">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -958,21 +950,19 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="43">
+  <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1006,7 +996,6 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -1046,8 +1035,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{22C8997C-2ABE-41DC-AB1A-FA6581138AA7}" name="Table3" displayName="Table3" ref="B47:D54" totalsRowShown="0">
-  <autoFilter ref="B47:D54" xr:uid="{22C8997C-2ABE-41DC-AB1A-FA6581138AA7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{22C8997C-2ABE-41DC-AB1A-FA6581138AA7}" name="Table3" displayName="Table3" ref="B47:D53" totalsRowShown="0">
+  <autoFilter ref="B47:D53" xr:uid="{22C8997C-2ABE-41DC-AB1A-FA6581138AA7}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{8E630765-9F53-45C2-818C-D26685EB5C1A}" name="Employee #"/>
     <tableColumn id="2" xr3:uid="{C455DF03-2D9D-4188-B674-5ED135AA9562}" name="Event Manager"/>
@@ -1058,8 +1047,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EEBECEE4-C806-4A6D-BF1F-07771520856E}" name="Table4" displayName="Table4" ref="B60:J69" totalsRowShown="0">
-  <autoFilter ref="B60:J69" xr:uid="{EEBECEE4-C806-4A6D-BF1F-07771520856E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{EEBECEE4-C806-4A6D-BF1F-07771520856E}" name="Table4" displayName="Table4" ref="B59:J68" totalsRowShown="0">
+  <autoFilter ref="B59:J68" xr:uid="{EEBECEE4-C806-4A6D-BF1F-07771520856E}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{811BDDC0-D94D-42E5-8718-F67C16A6E926}" name="Venue ID "/>
     <tableColumn id="2" xr3:uid="{9E1D2BC4-5DB5-45DA-B211-D1685251FC1E}" name="Venue Location"/>
@@ -1407,7 +1396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FA38BEC-78EC-44DC-83F3-AA711D021920}">
-  <dimension ref="A1:Q72"/>
+  <dimension ref="A1:Q71"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="1"/>
@@ -2408,418 +2397,406 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C48" t="s">
-        <v>105</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>106</v>
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C50" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D50" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C51" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C52" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B54" t="s">
-        <v>112</v>
-      </c>
-      <c r="C54" t="s">
-        <v>29</v>
-      </c>
-      <c r="D54" t="s">
         <v>41</v>
       </c>
     </row>
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A59" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>129</v>
+      <c r="B59" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="C59" t="s">
+        <v>113</v>
+      </c>
+      <c r="D59" t="s">
+        <v>130</v>
+      </c>
+      <c r="E59" t="s">
+        <v>131</v>
+      </c>
+      <c r="F59" t="s">
+        <v>132</v>
+      </c>
+      <c r="G59" t="s">
+        <v>133</v>
+      </c>
+      <c r="H59" t="s">
+        <v>134</v>
+      </c>
+      <c r="I59" t="s">
+        <v>94</v>
+      </c>
+      <c r="J59" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="5" t="s">
-        <v>135</v>
+      <c r="B60" t="s">
+        <v>116</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>4</v>
       </c>
       <c r="D60" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="E60" t="s">
-        <v>131</v>
+        <v>43</v>
       </c>
       <c r="F60" t="s">
-        <v>132</v>
-      </c>
-      <c r="G60" t="s">
-        <v>133</v>
+        <v>44</v>
+      </c>
+      <c r="G60">
+        <v>90026</v>
       </c>
       <c r="H60" t="s">
-        <v>134</v>
+        <v>98</v>
       </c>
       <c r="I60" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="J60" t="s">
-        <v>95</v>
+        <v>46</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C61" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D61" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E61" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F61" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G61">
-        <v>90026</v>
+        <v>78741</v>
       </c>
       <c r="H61" t="s">
-        <v>98</v>
+        <v>50</v>
       </c>
       <c r="I61" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="J61" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B62" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C62" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D62" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E62" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="F62" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G62">
-        <v>78741</v>
+        <v>90046</v>
       </c>
       <c r="H62" t="s">
-        <v>50</v>
+        <v>99</v>
       </c>
       <c r="I62" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="J62" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B63" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D63" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E63" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="F63" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="G63">
-        <v>90046</v>
+        <v>60616</v>
       </c>
       <c r="H63" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="I63" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="J63" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B64" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C64" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E64" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="F64" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G64">
-        <v>60616</v>
+        <v>10011</v>
       </c>
       <c r="H64" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="I64" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J64" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C65" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D65" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E65" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F65" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G65">
-        <v>10011</v>
+        <v>97214</v>
       </c>
       <c r="H65" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="I65" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="J65" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C66" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D66" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E66" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F66" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G66">
-        <v>97214</v>
+        <v>48226</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="I66" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="J66" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C67" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D67" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="E67" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="F67" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="G67">
-        <v>48226</v>
+        <v>10012</v>
       </c>
       <c r="H67" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="I67" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J67" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C68" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D68" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E68" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="F68" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="G68">
-        <v>10012</v>
+        <v>33132</v>
       </c>
       <c r="H68" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="I68" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="J68" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B69" t="s">
-        <v>123</v>
-      </c>
-      <c r="C69" t="s">
-        <v>34</v>
-      </c>
-      <c r="D69" t="s">
-        <v>84</v>
-      </c>
-      <c r="E69" t="s">
-        <v>85</v>
-      </c>
-      <c r="F69" t="s">
-        <v>86</v>
-      </c>
-      <c r="G69">
-        <v>33132</v>
-      </c>
-      <c r="H69" t="s">
-        <v>87</v>
-      </c>
-      <c r="I69" t="s">
-        <v>88</v>
-      </c>
-      <c r="J69" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B72" s="7" t="s">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B71" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="7"/>
-      <c r="I72" s="7"/>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="6"/>
+      <c r="F71" s="6"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="J19:J29">
     <sortCondition ref="J19:J29"/>
   </sortState>
   <mergeCells count="1">
-    <mergeCell ref="B72:I72"/>
+    <mergeCell ref="B71:I71"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="D48" r:id="rId1" display="larry.song@eventdoodle.com" xr:uid="{3D294303-FD95-442C-86A7-15790E32F076}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="4">
+    <tablePart r:id="rId1"/>
     <tablePart r:id="rId2"/>
     <tablePart r:id="rId3"/>
     <tablePart r:id="rId4"/>
-    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3064,20 +3041,21 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="ced60a7f-99b1-48d2-b555-34851c8026ae" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="9e0b35a9-e6cb-436b-81d4-4440ba439ca5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
+    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -3102,12 +3080,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EE6EC55-B0E7-4ACE-A5DA-E03DCA4973DE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D48FB9E6-6DE3-40FB-81F7-677295638F7C}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="ced60a7f-99b1-48d2-b555-34851c8026ae"/>
-    <ds:schemaRef ds:uri="9e0b35a9-e6cb-436b-81d4-4440ba439ca5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>